--- a/data/trans_orig/IP11A_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP11A_R-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -836,47 +836,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2839</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>4114</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>2839</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2839</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2839</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2839</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>4114</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>4114</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>4114</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2839</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2839</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2839</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,84 +1066,84 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1826</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>488</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4821</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,95%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>13,06%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>1826</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5207</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,95%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>14,1%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1826</t>
-        </is>
-      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
           <t>485</t>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>5124</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>35096</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>32101</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>36434</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>95,05%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>86,94%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,68%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>21046</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>35096</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>31715</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>36442</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>95,05%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>53049</t>
+          <t>52844</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>36922</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>36922</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>36922</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>21046</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>21046</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>21046</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>36922</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>36922</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>36922</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1522,47 +1522,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6764</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>10144</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>6764</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6764</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6764</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>6764</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>10144</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>10144</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>10144</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>6764</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>6764</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>6764</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,92 +1752,92 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1826</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>485</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4975</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,92%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10,69%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1826</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>481</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4861</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>10,45%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1826</t>
-        </is>
-      </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>488</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>4903</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>44699</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>41550</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>46040</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,08%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>89,31%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,96%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>35304</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>44699</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>41664</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>46044</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,08%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>76730</t>
+          <t>76926</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>81344</t>
+          <t>81341</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>46525</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>46525</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>46525</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>35304</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>35304</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>35304</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>46525</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>46525</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>46525</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2521</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6588</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>20,03%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4,97%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>52,35%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>710</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2834</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2702</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>17,51%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>69,91%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2521</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>638</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>20,03%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>5,07%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>66,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>722</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7135</t>
+          <t>6967</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>41,88%</t>
         </is>
       </c>
     </row>
@@ -2439,74 +2439,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10063</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5996</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>11958</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>79,97%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>47,65%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>95,03%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>3343</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1219</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1351</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>4053</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>82,49%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>30,09%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>33,34%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>10063</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>5779</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>11946</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>79,97%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>45,93%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>94,93%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>19</t>
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9502</t>
+          <t>9670</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15840</t>
+          <t>15915</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12584</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12584</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12584</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>4053</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>4053</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>4053</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>12584</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>12584</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>12584</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2782,47 +2782,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>44894</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>37951</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>44894</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>44894</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>44894</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>44894</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>37951</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>37951</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>37951</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>44894</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>44894</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>44894</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3125,47 +3125,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>15899</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>9708</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>15899</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>15899</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>15899</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>15899</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>9708</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>9708</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>9708</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>15899</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>15899</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>15899</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2521</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7305</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,96%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>710</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4234</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3544</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,37%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,19%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2521</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>632</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7867</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>713</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8323</t>
+          <t>8145</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -3468,74 +3468,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>70856</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>66072</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>72751</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,56%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>90,04%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,15%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>51002</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>47478</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>48168</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>51712</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,63%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>91,81%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>93,15%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>70856</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>65510</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>72745</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,56%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>89,28%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,14%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>176</t>
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>116766</t>
+          <t>116944</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>124377</t>
+          <t>124376</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>73377</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>73377</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>73377</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>51712</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>51712</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>51712</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>73377</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>73377</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>73377</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4047,42 +4047,42 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>2529</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>2457</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>2529</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4160,52 +4160,52 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>2529</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2529</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2529</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>2457</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>2457</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>2457</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2529</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2529</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2529</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2472</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,88%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2751</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>718</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6054</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>752</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5739</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>16,67%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,35%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>36,69%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2432</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1186</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6930</t>
+          <t>7538</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>15,74%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>30802</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>28918</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>31390</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,13%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,12%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>13749</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>10446</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>15782</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>10761</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>15748</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>83,33%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>63,31%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,65%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>30802</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>28958</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>31390</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,13%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>40960</t>
+          <t>40352</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>46704</t>
+          <t>46667</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,45%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>31390</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>31390</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>31390</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>16500</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>16500</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>16500</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>31390</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>31390</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>31390</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,107 +4615,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2901</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10,48%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>42,63%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>713</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2845</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>10,48%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3495</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>6,36%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>41,81%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3735</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>6,36%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>31,16%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6092</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3904</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>89,52%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>57,37%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>4412</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>6092</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>3960</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>89,52%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7483</t>
+          <t>7723</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>4412</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>4412</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>4412</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>6805</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4004</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,83%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2751</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>765</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6280</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>778</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6218</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>11,77%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,27%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>26,87%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1301</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4041</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1426</t>
+          <t>1428</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7423</t>
+          <t>8407</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>39423</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>36720</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>40724</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,81%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>90,17%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>20618</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>17089</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>22604</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>17151</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>22591</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>88,23%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>73,13%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,73%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>39423</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>36683</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>40724</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,81%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>56670</t>
+          <t>55686</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>62667</t>
+          <t>62665</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>40724</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>40724</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>40724</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>23369</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>23369</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>23369</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>40724</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>40724</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>40724</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5645,64 +5645,64 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1082</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1125</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1350</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -5720,7 +5720,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2432</t>
+          <t>2266</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1082</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1082</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1082</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>2432</t>
+          <t>2266</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2432</t>
+          <t>2266</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2432</t>
+          <t>2266</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>988</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -5890,12 +5890,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3123</t>
+          <t>4481</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,7 +5915,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>592</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -5925,12 +5925,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4274</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,7 +5950,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1602</t>
+          <t>1581</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -5960,12 +5960,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4964</t>
+          <t>5316</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>21,5%</t>
         </is>
       </c>
     </row>
@@ -5988,74 +5988,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12741</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9248</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>13729</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,8%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>67,36%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>10429</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>7896</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>11019</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>94,65%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>71,66%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>10400</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>7811</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>10992</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>94,61%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>71,06%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>13734</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>10472</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>14746</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>93,14%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>71,01%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>34</t>
@@ -6063,27 +6063,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>24163</t>
+          <t>23139</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>20801</t>
+          <t>19404</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25765</t>
+          <t>24720</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>13729</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>13729</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>13729</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>11019</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>11019</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>11019</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14746</t>
+          <t>10992</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14746</t>
+          <t>10992</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14746</t>
+          <t>10992</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>25765</t>
+          <t>24720</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>25765</t>
+          <t>24720</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>25765</t>
+          <t>24720</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,7 +6223,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>569</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3514</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>689</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -6268,12 +6268,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>2943</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1452</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4477</t>
+          <t>4153</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>33,36%</t>
         </is>
       </c>
     </row>
@@ -6331,74 +6331,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6813</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4331</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>7382</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>92,3%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>58,68%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>4297</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1528</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>5051</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>85,07%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>30,25%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>4379</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2122</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5068</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>86,41%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>41,87%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>7239</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>4577</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>7937</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>91,2%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>57,67%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>14</t>
@@ -6406,27 +6406,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>11536</t>
+          <t>11192</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8511</t>
+          <t>8296</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12988</t>
+          <t>12449</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7382</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7382</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>7382</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>5051</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>5051</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5051</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7937</t>
+          <t>5068</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7937</t>
+          <t>5068</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7937</t>
+          <t>5068</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>12988</t>
+          <t>12449</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12988</t>
+          <t>12449</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12988</t>
+          <t>12449</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>1557</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4444</t>
+          <t>5363</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5821</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>3054</t>
+          <t>2838</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>990</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7244</t>
+          <t>6628</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>16,81%</t>
         </is>
       </c>
     </row>
@@ -6674,74 +6674,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>20694</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>16888</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>22251</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>93,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>75,9%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>15807</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>12707</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>17151</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>92,17%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>74,09%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>15903</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>13129</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>17184</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>92,55%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>76,4%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>22324</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>18213</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>24034</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>92,88%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>75,78%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>51</t>
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>38131</t>
+          <t>36597</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33941</t>
+          <t>32807</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>40161</t>
+          <t>38445</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,49%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>22251</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>22251</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>22251</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>17151</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>17151</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>17151</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>24034</t>
+          <t>17184</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24034</t>
+          <t>17184</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24034</t>
+          <t>17184</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>41185</t>
+          <t>39435</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>41185</t>
+          <t>39435</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>41185</t>
+          <t>39435</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
